--- a/Document/Danh sách công việc elarning.xlsx
+++ b/Document/Danh sách công việc elarning.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buixu\Projects\fft_projects\elearning\Document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Projects\fftProjects\elearning_web\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AC4A20-8836-4983-A112-119DCDB12F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1576CD81-6813-422F-B736-B49EFDBE65E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23329FD4-C91A-4608-B710-537807E67C95}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23329FD4-C91A-4608-B710-537807E67C95}"/>
   </bookViews>
   <sheets>
     <sheet name="Các chức năng elearning" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="77">
   <si>
     <t>LandingPage</t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>Danh sách ví dụ</t>
-  </si>
-  <si>
-    <t>Phân quyền người dùng</t>
   </si>
   <si>
     <t>Quản lý học viên</t>
@@ -442,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -451,12 +448,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -472,122 +463,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -924,643 +925,639 @@
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="43"/>
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="37"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="10">
+        <v>1</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="43"/>
+      <c r="B4" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="37"/>
+      <c r="D4" s="46"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="10">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="43"/>
+      <c r="B5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="38"/>
+      <c r="D5" s="46"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="10">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="10">
+        <v>4</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="30"/>
+      <c r="B7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="10">
+        <v>5</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="43"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="47"/>
+      <c r="G9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="12">
+        <v>6</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="43"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="43"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="43"/>
+      <c r="B14" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="43"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="44"/>
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="49"/>
+      <c r="B20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="50"/>
+      <c r="B21" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="52"/>
+      <c r="B23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="53"/>
+      <c r="B24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="49"/>
+      <c r="B26" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="49"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="49"/>
+      <c r="B28" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="49"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="49"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="50"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="60"/>
+      <c r="B33" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="61"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="40"/>
+      <c r="B36" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="40"/>
+      <c r="B38" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="39"/>
+      <c r="D41" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="39"/>
+      <c r="D42" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="58"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="12">
-        <v>1</v>
-      </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="58"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="12">
-        <v>2</v>
-      </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="58"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="12">
-        <v>3</v>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="12">
-        <v>4</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
-      <c r="B7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="12">
-        <v>5</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="59"/>
-      <c r="G9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="14">
-        <v>6</v>
-      </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
-      <c r="B20" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="25" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="43"/>
-      <c r="B21" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="48"/>
-      <c r="B24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
-      <c r="B26" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
-      <c r="B28" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="45"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="43"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
-      <c r="B33" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="41"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="31"/>
-      <c r="D36" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40" s="31"/>
-      <c r="D40" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="28" t="s">
+      <c r="B43" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="C43" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="32"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="32"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="32"/>
+      <c r="B46" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C46" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="23" t="s">
+      <c r="D46" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="32"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="32"/>
+      <c r="B48" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="32"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="32"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="33"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
-      <c r="B46" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
-      <c r="B48" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D48" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="29"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" s="60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="30"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51" s="60" t="s">
-        <v>76</v>
+      <c r="D51" s="24" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="60" t="s">
-        <v>76</v>
-      </c>
+      <c r="A52" s="25"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -1575,6 +1572,8 @@
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B8:B9"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A43:A51"/>
@@ -1591,8 +1590,6 @@
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="A8:A16"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B8:B9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
